--- a/PCN_PCR_Settings.xlsx
+++ b/PCN_PCR_Settings.xlsx
@@ -493,7 +493,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Reflects app Ver 2.5 (2026-07-10). Regenerated by settings_xlsx.py in the pcr repo.</t>
+          <t>Reflects app Ver 2.7 (2026-07-10). Regenerated by settings_xlsx.py in the pcr repo.</t>
         </is>
       </c>
     </row>
